--- a/backend/platform/src/main/resources/jxls/resource_allocations_template.xlsx
+++ b/backend/platform/src/main/resources/jxls/resource_allocations_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm\hreasy\src\backend\platform\src\main\resources\jxls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BF9645-0101-4728-A272-91289FB94182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E55C19-5041-449C-92F4-6D93682AEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,22 +22,34 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>HR Easy</author>
     <author>Alexander Bondin</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{3C30748D-3FA5-427B-A083-2D3AC92B66CA}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="S6")</t>
+          <t>Alexander Bondin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+jx:area(lastCell="S6")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="1" shapeId="0" xr:uid="{A0140CB7-34D1-4C43-A972-B5937CD37668}">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{A0140CB7-34D1-4C43-A972-B5937CD37668}">
       <text>
         <r>
           <rPr>
@@ -247,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -325,19 +337,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -350,11 +372,482 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -395,468 +888,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -875,15 +906,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
+      <xdr:colOff>561975</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1895385</xdr:colOff>
+      <xdr:colOff>1876335</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>37650</xdr:rowOff>
+      <xdr:rowOff>56700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -903,7 +934,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="581025" y="76200"/>
+          <a:off x="561975" y="95250"/>
           <a:ext cx="1314360" cy="599625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -920,27 +951,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF67A8F5-29C9-4A8B-AB1E-BCA1EFC46B39}" name="Таблица1" displayName="Таблица1" ref="A5:S6" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF67A8F5-29C9-4A8B-AB1E-BCA1EFC46B39}" name="Таблица1" displayName="Таблица1" ref="A5:S6" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <tableColumns count="19">
-    <tableColumn id="20" xr3:uid="{474CFA14-D03F-430E-A165-18F82523D125}" name="Сотрудник" dataDxfId="19"/>
-    <tableColumn id="21" xr3:uid="{E2327C14-B53D-4AAA-91B8-B0CD13AC8183}" name="Email" dataDxfId="18"/>
-    <tableColumn id="1" xr3:uid="{4ADBDC2D-C5E2-4EAA-89CC-F8042723ACD1}" name="Бизнес-аккаунт" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{5A4718C9-71C8-4C66-AD3F-4801B020C8FB}" name="Проект" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{CBD16168-65AA-4C37-AF1B-5D807902B43F}" name="Направление" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{041EC8C5-D14C-4575-A540-DF5ADC197D33}" name="Роль на текущем проекте" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{5CD266E5-CAFA-417E-BAF8-C9D07B486E9C}" name="За год" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{F70FBB6E-865E-464C-AA81-82ED7E3B4D1C}" name="Январь" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{6AD2A470-0166-4739-9C98-19FB47FEE1D9}" name="Февраль" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{DE2D14F2-C7B5-44DC-9D89-91B478E67943}" name="Март" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{EF451081-DD51-43E0-B993-5EC655CEC751}" name="Апрель" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{5D393FCA-EF13-423E-9C0D-DF9426F56C8C}" name="Май" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{A68001C9-73A5-4886-AFBD-FCB2D5E6C2AF}" name="Июнь" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{BE5F7301-8D37-4378-B1FD-6B25B9DCE45B}" name="Июль" dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{A49C19B3-53A1-49D3-BD81-5778F79F177A}" name="Август" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{555767CE-2FF2-423C-8FB8-3F0901156F85}" name="Сентябрь" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{BDD956F7-F3CE-46F3-8E2F-518C452B40E1}" name="Октябрь" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{0BB7306B-EB2E-466A-9952-06660135577B}" name="Ноябрь" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{5B655832-AF92-4DFA-B5C6-BB713A77D09C}" name="Декабрь" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{474CFA14-D03F-430E-A165-18F82523D125}" name="Сотрудник" dataDxfId="18"/>
+    <tableColumn id="21" xr3:uid="{E2327C14-B53D-4AAA-91B8-B0CD13AC8183}" name="Email" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{4ADBDC2D-C5E2-4EAA-89CC-F8042723ACD1}" name="Бизнес-аккаунт" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{5A4718C9-71C8-4C66-AD3F-4801B020C8FB}" name="Проект" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{CBD16168-65AA-4C37-AF1B-5D807902B43F}" name="Направление" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{041EC8C5-D14C-4575-A540-DF5ADC197D33}" name="Роль на текущем проекте" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{5CD266E5-CAFA-417E-BAF8-C9D07B486E9C}" name="За год" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{F70FBB6E-865E-464C-AA81-82ED7E3B4D1C}" name="Январь" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{6AD2A470-0166-4739-9C98-19FB47FEE1D9}" name="Февраль" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{DE2D14F2-C7B5-44DC-9D89-91B478E67943}" name="Март" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{EF451081-DD51-43E0-B993-5EC655CEC751}" name="Апрель" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{5D393FCA-EF13-423E-9C0D-DF9426F56C8C}" name="Май" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{A68001C9-73A5-4886-AFBD-FCB2D5E6C2AF}" name="Июнь" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{BE5F7301-8D37-4378-B1FD-6B25B9DCE45B}" name="Июль" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{A49C19B3-53A1-49D3-BD81-5778F79F177A}" name="Август" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{555767CE-2FF2-423C-8FB8-3F0901156F85}" name="Сентябрь" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{BDD956F7-F3CE-46F3-8E2F-518C452B40E1}" name="Октябрь" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{0BB7306B-EB2E-466A-9952-06660135577B}" name="Ноябрь" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{5B655832-AF92-4DFA-B5C6-BB713A77D09C}" name="Декабрь" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1247,7 +1278,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="2" width="38.28515625" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
@@ -1256,165 +1287,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="35.25" customHeight="1">
-      <c r="A1" s="4"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="4"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="4"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
     </row>
     <row r="5" spans="1:19" ht="32.1" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="7" t="s">
+      <c r="S5" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="6" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
     <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="B2:S2"/>
+    <mergeCell ref="B3:S3"/>
+    <mergeCell ref="A4:S4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/backend/platform/src/main/resources/jxls/resource_allocations_template.xlsx
+++ b/backend/platform/src/main/resources/jxls/resource_allocations_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\stm\hreasy\src\backend\platform\src\main\resources\jxls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\stm\hreasy\src\hreasy\backend\platform\src\main\resources\jxls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E55C19-5041-449C-92F4-6D93682AEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542992ED-E938-4742-AC2C-429F60834AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="19515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аллокации" sheetId="1" r:id="rId1"/>
@@ -207,7 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -237,13 +237,6 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -259,22 +252,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -330,17 +312,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -356,10 +327,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -367,44 +338,45 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+  <dxfs count="24">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.##%"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -800,22 +772,18 @@
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -951,26 +919,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF67A8F5-29C9-4A8B-AB1E-BCA1EFC46B39}" name="Таблица1" displayName="Таблица1" ref="A5:S6" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF67A8F5-29C9-4A8B-AB1E-BCA1EFC46B39}" name="Таблица1" displayName="Таблица1" ref="A5:S6" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <tableColumns count="19">
-    <tableColumn id="20" xr3:uid="{474CFA14-D03F-430E-A165-18F82523D125}" name="Сотрудник" dataDxfId="18"/>
-    <tableColumn id="21" xr3:uid="{E2327C14-B53D-4AAA-91B8-B0CD13AC8183}" name="Email" dataDxfId="17"/>
-    <tableColumn id="1" xr3:uid="{4ADBDC2D-C5E2-4EAA-89CC-F8042723ACD1}" name="Бизнес-аккаунт" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{5A4718C9-71C8-4C66-AD3F-4801B020C8FB}" name="Проект" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{CBD16168-65AA-4C37-AF1B-5D807902B43F}" name="Направление" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{041EC8C5-D14C-4575-A540-DF5ADC197D33}" name="Роль на текущем проекте" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{5CD266E5-CAFA-417E-BAF8-C9D07B486E9C}" name="За год" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{F70FBB6E-865E-464C-AA81-82ED7E3B4D1C}" name="Январь" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{6AD2A470-0166-4739-9C98-19FB47FEE1D9}" name="Февраль" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{DE2D14F2-C7B5-44DC-9D89-91B478E67943}" name="Март" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{EF451081-DD51-43E0-B993-5EC655CEC751}" name="Апрель" dataDxfId="8"/>
-    <tableColumn id="12" xr3:uid="{5D393FCA-EF13-423E-9C0D-DF9426F56C8C}" name="Май" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{A68001C9-73A5-4886-AFBD-FCB2D5E6C2AF}" name="Июнь" dataDxfId="6"/>
-    <tableColumn id="14" xr3:uid="{BE5F7301-8D37-4378-B1FD-6B25B9DCE45B}" name="Июль" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{A49C19B3-53A1-49D3-BD81-5778F79F177A}" name="Август" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{555767CE-2FF2-423C-8FB8-3F0901156F85}" name="Сентябрь" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{BDD956F7-F3CE-46F3-8E2F-518C452B40E1}" name="Октябрь" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{0BB7306B-EB2E-466A-9952-06660135577B}" name="Ноябрь" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{474CFA14-D03F-430E-A165-18F82523D125}" name="Сотрудник" dataDxfId="19"/>
+    <tableColumn id="21" xr3:uid="{E2327C14-B53D-4AAA-91B8-B0CD13AC8183}" name="Email" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{4ADBDC2D-C5E2-4EAA-89CC-F8042723ACD1}" name="Бизнес-аккаунт" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{5A4718C9-71C8-4C66-AD3F-4801B020C8FB}" name="Проект" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{CBD16168-65AA-4C37-AF1B-5D807902B43F}" name="Направление" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{041EC8C5-D14C-4575-A540-DF5ADC197D33}" name="Роль на текущем проекте" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{5CD266E5-CAFA-417E-BAF8-C9D07B486E9C}" name="За год" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{F70FBB6E-865E-464C-AA81-82ED7E3B4D1C}" name="Январь" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{6AD2A470-0166-4739-9C98-19FB47FEE1D9}" name="Февраль" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{DE2D14F2-C7B5-44DC-9D89-91B478E67943}" name="Март" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{EF451081-DD51-43E0-B993-5EC655CEC751}" name="Апрель" dataDxfId="9"/>
+    <tableColumn id="12" xr3:uid="{5D393FCA-EF13-423E-9C0D-DF9426F56C8C}" name="Май" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{A68001C9-73A5-4886-AFBD-FCB2D5E6C2AF}" name="Июнь" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{BE5F7301-8D37-4378-B1FD-6B25B9DCE45B}" name="Июль" dataDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{A49C19B3-53A1-49D3-BD81-5778F79F177A}" name="Август" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{555767CE-2FF2-423C-8FB8-3F0901156F85}" name="Сентябрь" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{BDD956F7-F3CE-46F3-8E2F-518C452B40E1}" name="Октябрь" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{0BB7306B-EB2E-466A-9952-06660135577B}" name="Ноябрь" dataDxfId="2"/>
     <tableColumn id="19" xr3:uid="{5B655832-AF92-4DFA-B5C6-BB713A77D09C}" name="Декабрь" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -978,9 +946,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1018,7 +986,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1124,7 +1092,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1266,7 +1234,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1275,7 +1243,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="38.28515625" customWidth="1"/>
@@ -1286,172 +1254,172 @@
     <col min="7" max="19" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="35.25" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:19" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6"/>
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
     </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="7"/>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
     </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
     </row>
-    <row r="5" spans="1:19" ht="32.1" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:19" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="5" t="s">
@@ -1490,7 +1458,7 @@
       <c r="R6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="S6" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1502,6 +1470,11 @@
     <mergeCell ref="B3:S3"/>
     <mergeCell ref="A4:S4"/>
   </mergeCells>
+  <conditionalFormatting sqref="G6:S6">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$B$2="Единицы: Проценты"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
